--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,6 +1173,309 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128642046</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80216</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>816355</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7455851</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Noomi Berg, Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128642045</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>816299</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7455888</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Noomi Berg, Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128642047</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91453</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>816356</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7455852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Noomi Berg, Sonja Jederlund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91810</v>
+        <v>91816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80216</v>
+        <v>80220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91453</v>
+        <v>91458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>75175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R3" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B4" t="n">
-        <v>75175</v>
+        <v>82946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R4" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91816</v>
+        <v>91822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>75175</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R3" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>82946</v>
+        <v>75177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R4" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>91824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80220</v>
+        <v>80222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>75177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R3" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B4" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R4" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,6 +1480,103 @@
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128774119</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79708</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sweref99, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>816288</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7456009</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>75177</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R3" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>82948</v>
+        <v>75177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R4" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91825</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>80249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80249</v>
+        <v>80253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>75205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R3" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B4" t="n">
-        <v>75205</v>
+        <v>82979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R4" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91857</v>
+        <v>91862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128489524</v>
+        <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>816357</v>
+        <v>816257</v>
       </c>
       <c r="R3" t="n">
-        <v>7455840</v>
+        <v>7455993</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128489480</v>
+        <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>82979</v>
+        <v>75209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>816257</v>
+        <v>816357</v>
       </c>
       <c r="R4" t="n">
-        <v>7455993</v>
+        <v>7455840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128489483</v>
       </c>
       <c r="B2" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>128489480</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>128489524</v>
       </c>
       <c r="B4" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>128489482</v>
       </c>
       <c r="B5" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>128489481</v>
       </c>
       <c r="B6" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80162</v>
+        <v>80167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>128642046</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>128642045</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128642047</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2021 artfynd.xlsx
+++ b/artfynd/A 30542-2021 artfynd.xlsx
@@ -1486,7 +1486,7 @@
         <v>128774119</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
